--- a/наценки по группам товара.xlsx
+++ b/наценки по группам товара.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.7109375" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2220,8 +2219,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127"/>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="15" t="inlineStr">
         <is>
@@ -2229,7 +2226,6 @@
         </is>
       </c>
     </row>
-    <row r="129"/>
     <row r="130" ht="15.75" customHeight="1" thickBot="1">
       <c r="A130" s="16" t="inlineStr">
         <is>
@@ -2610,6 +2606,114 @@
       </c>
       <c r="D150" s="27" t="n">
         <v>10550</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B151" s="26" t="inlineStr">
+        <is>
+          <t>UT-00248359</t>
+        </is>
+      </c>
+      <c r="C151" s="26" t="inlineStr">
+        <is>
+          <t>Морозильный ларь HOMELINE HCF-215 ( t+8*-30* .2 корзины  85*56,5*85)</t>
+        </is>
+      </c>
+      <c r="D151" s="27" t="n">
+        <v>18290</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B152" s="26" t="inlineStr">
+        <is>
+          <t>UT-00248319</t>
+        </is>
+      </c>
+      <c r="C152" s="26" t="inlineStr">
+        <is>
+          <t>Морозильный ларь HOMELINE HCF-215# ( t+8*-30* 85*56,5*85 )</t>
+        </is>
+      </c>
+      <c r="D152" s="27" t="n">
+        <v>18290</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B153" s="26" t="inlineStr">
+        <is>
+          <t>UT-00248361</t>
+        </is>
+      </c>
+      <c r="C153" s="26" t="inlineStr">
+        <is>
+          <t>Морозильный ларь HOMELINE HCF-285 ( t+8*-30*. 2 корзины замок ключ  113*60*85)</t>
+        </is>
+      </c>
+      <c r="D153" s="27" t="n">
+        <v>24990</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B154" s="26" t="inlineStr">
+        <is>
+          <t>UT-00248322</t>
+        </is>
+      </c>
+      <c r="C154" s="26" t="inlineStr">
+        <is>
+          <t>Морозильный ларь HOMELINE HCF-285# ( t+8*-30* замок ключ 113*60*85)</t>
+        </is>
+      </c>
+      <c r="D154" s="27" t="n">
+        <v>24990</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B155" s="26" t="inlineStr">
+        <is>
+          <t>UT-00248363</t>
+        </is>
+      </c>
+      <c r="C155" s="26" t="inlineStr">
+        <is>
+          <t>Морозильный ларь HOMELINE HCF-415 ( t+8*-30*. 3 корзины 1365*740*870 )</t>
+        </is>
+      </c>
+      <c r="D155" s="27" t="n">
+        <v>33990</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B156" s="26" t="inlineStr">
+        <is>
+          <t>UT-00248323</t>
+        </is>
+      </c>
+      <c r="C156" s="26" t="inlineStr">
+        <is>
+          <t>Морозильный ларь HOMELINE HCF-415# ( t+8*-30* 3 корзины 1365*740*870 )</t>
+        </is>
+      </c>
+      <c r="D156" s="27" t="n">
+        <v>33990</v>
       </c>
     </row>
   </sheetData>

--- a/наценки по группам товара.xlsx
+++ b/наценки по группам товара.xlsx
@@ -616,6 +616,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2219,6 +2220,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="126"/>
+    <row r="127"/>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="15" t="inlineStr">
         <is>
@@ -2226,6 +2229,7 @@
         </is>
       </c>
     </row>
+    <row r="129"/>
     <row r="130" ht="15.75" customHeight="1" thickBot="1">
       <c r="A130" s="16" t="inlineStr">
         <is>
@@ -2443,7 +2447,7 @@
         </is>
       </c>
       <c r="D141" s="22" t="n">
-        <v>19550</v>
+        <v>18350</v>
       </c>
     </row>
     <row r="142" ht="64.5" customHeight="1">
@@ -2461,7 +2465,7 @@
         </is>
       </c>
       <c r="D142" s="22" t="n">
-        <v>19550</v>
+        <v>18350</v>
       </c>
     </row>
     <row r="143" ht="64.5" customHeight="1">
@@ -2515,7 +2519,7 @@
         </is>
       </c>
       <c r="D145" s="22" t="n">
-        <v>17950</v>
+        <v>18350</v>
       </c>
     </row>
     <row r="146" ht="51.75" customHeight="1">
@@ -2533,7 +2537,7 @@
         </is>
       </c>
       <c r="D146" s="22" t="n">
-        <v>17950</v>
+        <v>18350</v>
       </c>
     </row>
     <row r="147" ht="51.75" customHeight="1">
@@ -2623,7 +2627,7 @@
         </is>
       </c>
       <c r="D151" s="27" t="n">
-        <v>18290</v>
+        <v>17550</v>
       </c>
     </row>
     <row r="152">
@@ -2641,7 +2645,7 @@
         </is>
       </c>
       <c r="D152" s="27" t="n">
-        <v>18290</v>
+        <v>17550</v>
       </c>
     </row>
     <row r="153">
@@ -2659,7 +2663,7 @@
         </is>
       </c>
       <c r="D153" s="27" t="n">
-        <v>24990</v>
+        <v>24550</v>
       </c>
     </row>
     <row r="154">
@@ -2677,7 +2681,7 @@
         </is>
       </c>
       <c r="D154" s="27" t="n">
-        <v>24990</v>
+        <v>24550</v>
       </c>
     </row>
     <row r="155">
@@ -2695,7 +2699,7 @@
         </is>
       </c>
       <c r="D155" s="27" t="n">
-        <v>33990</v>
+        <v>32350</v>
       </c>
     </row>
     <row r="156">
@@ -2713,7 +2717,7 @@
         </is>
       </c>
       <c r="D156" s="27" t="n">
-        <v>33990</v>
+        <v>32350</v>
       </c>
     </row>
   </sheetData>
